--- a/output/第10期計画_将来推計_第2段階_サービス見込量.xlsx
+++ b/output/第10期計画_将来推計_第2段階_サービス見込量.xlsx
@@ -7133,7 +7133,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>施設・居住系の見込量は定員を超えて実現しない。居所変更実態調査で把握した定員及び入所者数と突合する。</t>
+          <t>施設・居住系の見込量は定員を超えて実現しない。居所変更実態調査で把握した定員及び入所者数と突合する。特定施設の定員は、令和8年8月4日に受領した北海道の届出済有料老人ホーム一覧（令和8年7月1日現在）により58人から156人に改めた（住まいと施設の公表名簿との突合 03シート）。</t>
         </is>
       </c>
     </row>
@@ -7145,22 +7145,26 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>施設数</t>
+          <t>調査の
+回答数</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>定員</t>
+          <t>調査の
+定員</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>入所者</t>
+          <t>名簿等による
+定員</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>入所率</t>
+          <t>調査の
+入所者</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -7174,7 +7178,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>特養・地域密着型特養</t>
@@ -7186,24 +7190,24 @@
       <c r="C5" s="7" t="n">
         <v>152</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>調査による</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n">
         <v>146</v>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>96.1％</t>
-        </is>
       </c>
       <c r="F5" s="7" t="n">
         <v>6</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>特別養護老人ホーム美瑛慈光園の入所者数が未記入のため、要介護度別の内訳58人を加えた</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
+          <t>特別養護老人ホーム美瑛慈光園の入所者数が未記入のため、要介護度別の内訳58人を加えた。見える化K1a・K1bは各3事業所であり、計2施設が未回答である</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>介護老人保健施設</t>
@@ -7215,20 +7219,24 @@
       <c r="C6" s="7" t="n">
         <v>240</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>調査による</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
         <v>201</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>83.8％</t>
-        </is>
       </c>
       <c r="F6" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="G6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>見える化K1c（3事業所）と一致し、区域内のすべてを把握している</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>グループホーム</t>
@@ -7240,20 +7248,24 @@
       <c r="C7" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>調査による</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
         <v>75</v>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>92.6％</t>
-        </is>
       </c>
       <c r="F7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="7" t="inlineStr"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>見える化K2c（5事業所）と一致し、区域内のすべてを把握している</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>特定施設</t>
@@ -7265,23 +7277,29 @@
       <c r="C8" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>57</v>
+      <c r="D8" s="16" t="n">
+        <v>156</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>98.3％</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
+          <t>57（2施設分）</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>北海道の届出済有料老人ホーム一覧による3施設の定員。調査に回答したのは2施設（58人）で、さわやか東神楽館（東神楽町・100人）が回答していない。入所者数は回答した2施設分のみであり、入所率は算定できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>住宅型有料・サ高住</t>
+          <t>住宅型有料・サ高住・軽費</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
@@ -7290,20 +7308,26 @@
       <c r="C9" s="7" t="n">
         <v>121</v>
       </c>
-      <c r="D9" s="7" t="n">
-        <v>115</v>
+      <c r="D9" s="16" t="n">
+        <v>339</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>95.0％</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
+          <t>115（4施設分）</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>北海道の名簿による住宅型有料9施設223人・サービス付き高齢者向け住宅2件66戸・軽費老人ホーム1施設50人。調査に回答したのは4施設で、入所率は算定できない。介護保険の指定サービスではないため見込量には含まれない</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>計</t>
@@ -7316,17 +7340,23 @@
         <v>652</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>594</v>
+        <v>968</v>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>91.1％</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>58</v>
-      </c>
-      <c r="G10" s="9" t="inlineStr"/>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>名簿等による定員は、介護保険の指定を受ける施設・居住系（特養・老健・グループホーム・特定施設）と指定を受けない住まいを合わせたものである</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -7426,28 +7456,28 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>139</v>
+        <v>237</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>104.6％</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>定員超過</t>
+          <t>61.4％</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>定員内</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>整備又は上限の判断を要する</t>
+          <t>定員に余裕がある</t>
         </is>
       </c>
     </row>
     <row r="17" ht="104" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>注1）調査で把握した定員652人・入所者594人（美瑛慈光園の58人を含む）は、居所変更実態調査に回答した18施設分である。見える化K系列では特別養護老人ホーム3・地域密着型特別養護老人ホーム3・介護老人保健施設3・特定施設3・グループホーム5であり、特養と地域密着型特養で計2施設が未回答である（3調査の点検 10シート）。定員の全体像は未回答2施設を加える必要がある。注2）居住系サービスの利用者数（令和11年度145人）は区域内の定員139人（グループホーム81人＋特定施設58人）を上回る。これは令和7年度の実績（144人）でも同じであり、区域外の居住系施設を利用している分が含まれているためと考えられる。介護サービス自給率（δ）で施設・居住系の区域外利用が東川町23.2％・美瑛町24.7％・東神楽町34.5％であることと整合する。定員による制約としてではなく、区域外利用の構造として読む。施設サービスは定員392人に対し339人であり余裕がある。注3）住宅型有料老人ホーム・サービス付高齢者向け住宅は介護保険の指定サービスではないため、見込量（居住系サービス）には含まれない。定員121人・入居者115人は住まいの供給量として第2章第3節に掲載する。注4）第6章第4節（施設等の整備の方針）では、待機者数（重複を除くと82人・3調査の点検No.13）と本表の空き（58人）を対照して判断する。</t>
+          <t>注1）調査で把握した定員652人・入所者594人（美瑛慈光園の58人を含む）は、居所変更実態調査に回答した18施設分である。見える化K系列では特別養護老人ホーム3・地域密着型特別養護老人ホーム3・介護老人保健施設3・特定施設3・グループホーム5であり、特養と地域密着型特養で計2施設が未回答である（3調査の点検 10シート）。定員の全体像は未回答2施設を加える必要がある。注2）居住系サービスの区域内定員は237人（グループホーム81人＋特定施設156人）であり、令和11年度の見込量145人は定員内に収まる。特定施設の定員は当初、居所変更実態調査に回答した2施設分の58人としていたが、北海道の届出済有料老人ホーム一覧により3施設156人であることが確認された（さわやか東神楽館100人が調査に回答していない）。見える化K2a（特定施設入居者生活介護の事業所数3）とも一致する。定員に余裕があるため、居住系は定員による制約を受けない。なお区域内の施設には住所地特例により他の保険者の被保険者も入居しており、定員と見込量の差がそのまま空きを示すものではない。居所変更実態調査では特定施設の新規入所の84.2％が区域外からの入所であった。施設サービスは定員392人に対し339人であり余裕がある。注3）住宅型有料老人ホーム・サービス付高齢者向け住宅・軽費老人ホームは介護保険の指定サービスではないため、見込量（居住系サービス）には含まれない。北海道の名簿により、区域内には住宅型有料老人ホーム9施設・定員223人、サービス付き高齢者向け住宅2件・66戸、軽費老人ホーム1施設・50人があることが確認された。住まいの供給量として第2章第3節に掲載する（住まいと施設の公表名簿との突合 04シート）。注4）第6章第4節（施設等の整備の方針）では、待機者数（重複を除くと82人・3調査の点検No.13）と本表の空き（58人）を対照して判断する。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_将来推計_第2段階_サービス見込量.xlsx
+++ b/output/第10期計画_将来推計_第2段階_サービス見込量.xlsx
@@ -7190,20 +7190,22 @@
       <c r="C5" s="7" t="n">
         <v>152</v>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>調査による</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>146</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>6</v>
+      <c r="D5" s="16" t="n">
+        <v>222</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>146（4施設分）</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>特別養護老人ホーム美瑛慈光園の入所者数が未記入のため、要介護度別の内訳58人を加えた。見える化K1a・K1bは各3事業所であり、計2施設が未回答である</t>
+          <t>北海道の特別養護老人ホーム名簿（令和8年7月1日現在）による介護老人福祉施設3施設160人＋地域密着型3施設62人。見える化K1a・K1bの各3事業所と一致する。調査には東神楽町特別養護老人ホームアゼリアハイツ（広域型50人・ユニット型20人）が回答していない</t>
         </is>
       </c>
     </row>
@@ -7261,7 +7263,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>見える化K2c（5事業所）と一致し、区域内のすべてを把握している</t>
+          <t>見える化K2c（令和6年度5事業所）とは一致するが、北海道の介護保険事業所一覧（令和8年6月30日現在）は7事業所である。新たな2事業所（ファミリー・くるみの郷。いずれも東川町）は定員が不明であり、調査の81人に算入していない</t>
         </is>
       </c>
     </row>
@@ -7340,7 +7342,7 @@
         <v>652</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>968</v>
+        <v>1038</v>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
@@ -7421,11 +7423,11 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>392</v>
+        <v>462</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>86.4％</t>
+          <t>73.3％</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
@@ -7477,7 +7479,7 @@
     <row r="17" ht="104" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>注1）調査で把握した定員652人・入所者594人（美瑛慈光園の58人を含む）は、居所変更実態調査に回答した18施設分である。見える化K系列では特別養護老人ホーム3・地域密着型特別養護老人ホーム3・介護老人保健施設3・特定施設3・グループホーム5であり、特養と地域密着型特養で計2施設が未回答である（3調査の点検 10シート）。定員の全体像は未回答2施設を加える必要がある。注2）居住系サービスの区域内定員は237人（グループホーム81人＋特定施設156人）であり、令和11年度の見込量145人は定員内に収まる。特定施設の定員は当初、居所変更実態調査に回答した2施設分の58人としていたが、北海道の届出済有料老人ホーム一覧により3施設156人であることが確認された（さわやか東神楽館100人が調査に回答していない）。見える化K2a（特定施設入居者生活介護の事業所数3）とも一致する。定員に余裕があるため、居住系は定員による制約を受けない。なお区域内の施設には住所地特例により他の保険者の被保険者も入居しており、定員と見込量の差がそのまま空きを示すものではない。居所変更実態調査では特定施設の新規入所の84.2％が区域外からの入所であった。施設サービスは定員392人に対し339人であり余裕がある。注3）住宅型有料老人ホーム・サービス付高齢者向け住宅・軽費老人ホームは介護保険の指定サービスではないため、見込量（居住系サービス）には含まれない。北海道の名簿により、区域内には住宅型有料老人ホーム9施設・定員223人、サービス付き高齢者向け住宅2件・66戸、軽費老人ホーム1施設・50人があることが確認された。住まいの供給量として第2章第3節に掲載する（住まいと施設の公表名簿との突合 04シート）。注4）第6章第4節（施設等の整備の方針）では、待機者数（重複を除くと82人・3調査の点検No.13）と本表の空き（58人）を対照して判断する。</t>
+          <t>注0）居住系の定員には、令和8年6月30日現在で7事業所となっているグループホームのうち、調査で把握した5事業所81人のみを算入している。新たな2事業所（ファミリー・くるみの郷）の定員が不明であるため、定員の余裕は本表よりさらに大きい。注1）調査で把握した定員652人・入所者594人（美瑛慈光園の58人を含む）は、居所変更実態調査に回答した18施設分である。見える化K系列では特別養護老人ホーム3・地域密着型特別養護老人ホーム3・介護老人保健施設3・特定施設3・グループホーム5であり、特養と地域密着型特養で計2施設が未回答である（3調査の点検 10シート）。定員の全体像は未回答2施設を加える必要がある。注2）居住系サービスの区域内定員は237人（グループホーム81人＋特定施設156人）であり、令和11年度の見込量145人は定員内に収まる。特定施設の定員は当初、居所変更実態調査に回答した2施設分の58人としていたが、北海道の届出済有料老人ホーム一覧により3施設156人であることが確認された（さわやか東神楽館100人が調査に回答していない）。見える化K2a（特定施設入居者生活介護の事業所数3）とも一致する。定員に余裕があるため、居住系は定員による制約を受けない。なお区域内の施設には住所地特例により他の保険者の被保険者も入居しており、定員と見込量の差がそのまま空きを示すものではない。居所変更実態調査では特定施設の新規入所の84.2％が区域外からの入所であった。施設サービスは定員462人（特養160人・地域密着型特養62人・老健240人）に対し339人であり余裕がある。特養の定員は北海道の特別養護老人ホーム名簿により確定した（住まいと施設の公表名簿との突合 09シート）。注3）住宅型有料老人ホーム・サービス付高齢者向け住宅・軽費老人ホームは介護保険の指定サービスではないため、見込量（居住系サービス）には含まれない。北海道の名簿により、区域内には住宅型有料老人ホーム9施設・定員223人、サービス付き高齢者向け住宅2件・66戸、軽費老人ホーム1施設・50人があることが確認された。住まいの供給量として第2章第3節に掲載する（住まいと施設の公表名簿との突合 04シート）。注4）第6章第4節（施設等の整備の方針）では、待機者数（重複を除くと82人・3調査の点検No.13）と本表の空き（58人）を対照して判断する。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_将来推計_第2段階_サービス見込量.xlsx
+++ b/output/第10期計画_将来推計_第2段階_サービス見込量.xlsx
@@ -7250,20 +7250,22 @@
       <c r="C7" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>調査による</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>6</v>
+      <c r="D7" s="16" t="n">
+        <v>99</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>75（5施設分）</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>見える化K2c（令和6年度5事業所）とは一致するが、北海道の介護保険事業所一覧（令和8年6月30日現在）は7事業所である。新たな2事業所（ファミリー・くるみの郷。いずれも東川町）は定員が不明であり、調査の81人に算入していない</t>
+          <t>北海道の介護保険事業所一覧（令和8年6月30日現在）は7事業所である。調査で把握した5事業所81人に、介護サービス情報公表システムの個別画面により確認したグループホームファミリー18人を加えて99人とした。くるみの郷（東川町）は公表システムに掲載がなく、定員が未確定である</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7344,7 @@
         <v>652</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>1038</v>
+        <v>1056</v>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
@@ -7458,11 +7460,11 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>61.4％</t>
+          <t>57.0％</t>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">
@@ -7479,7 +7481,7 @@
     <row r="17" ht="104" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>注0）居住系の定員には、令和8年6月30日現在で7事業所となっているグループホームのうち、調査で把握した5事業所81人のみを算入している。新たな2事業所（ファミリー・くるみの郷）の定員が不明であるため、定員の余裕は本表よりさらに大きい。注1）調査で把握した定員652人・入所者594人（美瑛慈光園の58人を含む）は、居所変更実態調査に回答した18施設分である。見える化K系列では特別養護老人ホーム3・地域密着型特別養護老人ホーム3・介護老人保健施設3・特定施設3・グループホーム5であり、特養と地域密着型特養で計2施設が未回答である（3調査の点検 10シート）。定員の全体像は未回答2施設を加える必要がある。注2）居住系サービスの区域内定員は237人（グループホーム81人＋特定施設156人）であり、令和11年度の見込量145人は定員内に収まる。特定施設の定員は当初、居所変更実態調査に回答した2施設分の58人としていたが、北海道の届出済有料老人ホーム一覧により3施設156人であることが確認された（さわやか東神楽館100人が調査に回答していない）。見える化K2a（特定施設入居者生活介護の事業所数3）とも一致する。定員に余裕があるため、居住系は定員による制約を受けない。なお区域内の施設には住所地特例により他の保険者の被保険者も入居しており、定員と見込量の差がそのまま空きを示すものではない。居所変更実態調査では特定施設の新規入所の84.2％が区域外からの入所であった。施設サービスは定員462人（特養160人・地域密着型特養62人・老健240人）に対し339人であり余裕がある。特養の定員は北海道の特別養護老人ホーム名簿により確定した（住まいと施設の公表名簿との突合 09シート）。注3）住宅型有料老人ホーム・サービス付高齢者向け住宅・軽費老人ホームは介護保険の指定サービスではないため、見込量（居住系サービス）には含まれない。北海道の名簿により、区域内には住宅型有料老人ホーム9施設・定員223人、サービス付き高齢者向け住宅2件・66戸、軽費老人ホーム1施設・50人があることが確認された。住まいの供給量として第2章第3節に掲載する（住まいと施設の公表名簿との突合 04シート）。注4）第6章第4節（施設等の整備の方針）では、待機者数（重複を除くと82人・3調査の点検No.13）と本表の空き（58人）を対照して判断する。</t>
+          <t>注0）グループホームの定員99人は、居所変更実態調査で把握した5事業所81人に、介護サービス情報公表システムの個別画面により確認したグループホームファミリー（東川町・2ユニット18人）を加えたものである。くるみの郷（東川町）は公表システムに掲載がなく定員が未確定であるため、含めていない。定員の余裕は本表よりさらに大きい（住まいと施設の公表名簿との突合 10シート）。注1）調査で把握した定員652人・入所者594人（美瑛慈光園の58人を含む）は、居所変更実態調査に回答した18施設分である。見える化K系列では特別養護老人ホーム3・地域密着型特別養護老人ホーム3・介護老人保健施設3・特定施設3・グループホーム5であり、特養と地域密着型特養で計2施設が未回答である（3調査の点検 10シート）。定員の全体像は未回答2施設を加える必要がある。注2）居住系サービスの区域内定員は255人（グループホーム99人＋特定施設156人）であり、令和11年度の見込量145人は定員内に収まる。特定施設の定員は当初、居所変更実態調査に回答した2施設分の58人としていたが、北海道の届出済有料老人ホーム一覧により3施設156人であることが確認された（さわやか東神楽館100人が調査に回答していない）。見える化K2a（特定施設入居者生活介護の事業所数3）とも一致する。定員に余裕があるため、居住系は定員による制約を受けない。なお区域内の施設には住所地特例により他の保険者の被保険者も入居しており、定員と見込量の差がそのまま空きを示すものではない。居所変更実態調査では特定施設の新規入所の84.2％が区域外からの入所であった。施設サービスは定員462人（特養160人・地域密着型特養62人・老健240人）に対し339人であり余裕がある。特養の定員は北海道の特別養護老人ホーム名簿により確定した（住まいと施設の公表名簿との突合 09シート）。注3）住宅型有料老人ホーム・サービス付高齢者向け住宅・軽費老人ホームは介護保険の指定サービスではないため、見込量（居住系サービス）には含まれない。北海道の名簿により、区域内には住宅型有料老人ホーム9施設・定員223人、サービス付き高齢者向け住宅2件・66戸、軽費老人ホーム1施設・50人があることが確認された。住まいの供給量として第2章第3節に掲載する（住まいと施設の公表名簿との突合 04シート）。注4）第6章第4節（施設等の整備の方針）では、待機者数（重複を除くと82人・3調査の点検No.13）と本表の空き（58人）を対照して判断する。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_将来推計_第2段階_サービス見込量.xlsx
+++ b/output/第10期計画_将来推計_第2段階_サービス見込量.xlsx
@@ -7668,7 +7668,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>第5章の施策により利用率を上げる目標を立てる場合は、見込量に上乗せする必要がある。未利用の理由は資料依頼No.7で照会中である。</t>
+          <t>第5章の施策により利用率を上げる目標を立てる場合は、見込量に上乗せする必要がある。未利用の理由は資料依頼No.8で照会中である。</t>
         </is>
       </c>
       <c r="E9" s="17" t="inlineStr">

--- a/output/第10期計画_将来推計_第2段階_サービス見込量.xlsx
+++ b/output/第10期計画_将来推計_第2段階_サービス見込量.xlsx
@@ -812,17 +812,17 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1059</t>
         </is>
       </c>
     </row>
@@ -839,17 +839,17 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>147</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>148</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>150</t>
         </is>
       </c>
     </row>
@@ -866,17 +866,17 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>342</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>346</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>349</t>
         </is>
       </c>
     </row>
@@ -893,17 +893,17 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1558</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2067</t>
         </is>
       </c>
     </row>
@@ -947,17 +947,17 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>499</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>504</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>509</t>
         </is>
       </c>
     </row>
@@ -1259,42 +1259,42 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>307</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>301</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>531</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>308</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>218</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr"/>
@@ -1307,42 +1307,42 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>312</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>306</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>539</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>313</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>223</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>162</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr"/>
@@ -1355,42 +1355,42 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>317</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>310</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>547</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>318</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr"/>
@@ -1506,42 +1506,42 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>304</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>298</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>526</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>217</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>158</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr"/>
@@ -1554,42 +1554,42 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>307</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>301</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>531</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>308</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr"/>
@@ -1602,42 +1602,42 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>311</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>304</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>537</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>312</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>162</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr"/>
@@ -1753,42 +1753,42 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>312</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>306</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>540</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>313</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>223</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>162</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr"/>
@@ -1801,42 +1801,42 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>320</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>313</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>552</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>321</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>166</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr"/>
@@ -1849,42 +1849,42 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>327</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>321</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>565</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>328</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr"/>
@@ -2213,42 +2213,42 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>106.7</t>
+          <t>108.3</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>168.5</t>
+          <t>171.1</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>339.7</t>
+          <t>344.8</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>190.3</t>
+          <t>193.2</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>1021.8</t>
+          <t>1037.3</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr"/>
@@ -2262,42 +2262,42 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>106.9</t>
+          <t>109.4</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>168.9</t>
+          <t>172.9</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>340.5</t>
+          <t>348.4</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>190.8</t>
+          <t>195.2</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>1024.4</t>
+          <t>1048.1</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr"/>
@@ -2311,42 +2311,42 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>110.6</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>169.3</t>
+          <t>174.7</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>341.3</t>
+          <t>352.0</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>191.2</t>
+          <t>197.2</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>1026.8</t>
+          <t>1059.0</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr"/>
@@ -2416,42 +2416,42 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>146.9</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr"/>
@@ -2465,42 +2465,42 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>145.1</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr"/>
@@ -2514,42 +2514,42 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>145.4</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr"/>
@@ -2629,32 +2629,32 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.4</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>337.0</t>
+          <t>342.1</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr"/>
@@ -2678,32 +2678,32 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>100.4</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>337.8</t>
+          <t>345.6</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr"/>
@@ -2727,32 +2727,32 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>338.6</t>
+          <t>349.2</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr"/>
@@ -3548,32 +3548,32 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>100.4</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>273.9</t>
+          <t>278.1</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr"/>
@@ -3638,42 +3638,42 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>155.2</t>
+          <t>157.6</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr"/>
@@ -3693,22 +3693,22 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr"/>
@@ -3738,42 +3738,42 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>191.8</t>
+          <t>194.7</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr"/>
@@ -3798,22 +3798,22 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr"/>
@@ -3838,42 +3838,42 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>100.4</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>283.1</t>
+          <t>287.4</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr"/>
@@ -3898,12 +3898,12 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr"/>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr"/>
@@ -3988,42 +3988,42 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>118.7</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>182.6</t>
+          <t>185.4</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>127.8</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>648.3</t>
+          <t>658.2</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr"/>
@@ -4043,22 +4043,22 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>100.4</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr"/>
@@ -4098,17 +4098,17 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="J32" s="7" t="inlineStr"/>
@@ -4205,32 +4205,32 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>100.7</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>281.0</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr"/>
@@ -4295,42 +4295,42 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>155.6</t>
+          <t>159.2</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr"/>
@@ -4350,22 +4350,22 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -4375,12 +4375,12 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr"/>
@@ -4395,42 +4395,42 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>192.2</t>
+          <t>196.7</t>
         </is>
       </c>
       <c r="J40" s="7" t="inlineStr"/>
@@ -4455,22 +4455,22 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr"/>
@@ -4495,42 +4495,42 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>100.7</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>283.8</t>
+          <t>290.4</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr"/>
@@ -4555,12 +4555,12 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr"/>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="J44" s="7" t="inlineStr"/>
@@ -4645,42 +4645,42 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>121.8</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>183.1</t>
+          <t>187.3</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>131.1</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>650.0</t>
+          <t>665.0</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr"/>
@@ -4700,22 +4700,22 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>100.7</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr"/>
@@ -4755,17 +4755,17 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr"/>
@@ -4862,32 +4862,32 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>100.9</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>275.3</t>
+          <t>283.9</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr"/>
@@ -4952,42 +4952,42 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>160.9</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr"/>
@@ -5007,22 +5007,22 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="J54" s="7" t="inlineStr"/>
@@ -5052,42 +5052,42 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>192.7</t>
+          <t>198.7</t>
         </is>
       </c>
       <c r="J55" s="7" t="inlineStr"/>
@@ -5112,22 +5112,22 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr"/>
@@ -5152,42 +5152,42 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>100.9</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>284.4</t>
+          <t>293.4</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr"/>
@@ -5212,12 +5212,12 @@
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="J58" s="7" t="inlineStr"/>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr"/>
@@ -5302,42 +5302,42 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>119.3</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>189.3</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>651.5</t>
+          <t>671.9</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr"/>
@@ -5357,22 +5357,22 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>100.9</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr"/>
@@ -5412,17 +5412,17 @@
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr"/>
@@ -5563,22 +5563,22 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>15569</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>16136</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>+1.0％</t>
+          <t>+4.2％</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr"/>
@@ -5647,22 +5647,22 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>+1.0％</t>
+          <t>+4.2％</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr"/>
@@ -5687,22 +5687,22 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>769</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>777</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>786</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>+1.0％</t>
+          <t>+4.2％</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
@@ -5727,22 +5727,22 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>695</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>710</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>+1.0％</t>
+          <t>+4.2％</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr"/>
@@ -5767,22 +5767,22 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>+1.0％</t>
+          <t>+4.2％</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
@@ -5807,22 +5807,22 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>213</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>215</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>218</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>+1.0％</t>
+          <t>+4.2％</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr"/>
@@ -5852,17 +5852,17 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>+1.0％</t>
+          <t>+4.2％</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr"/>
@@ -5887,22 +5887,22 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>575</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>581</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>587</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>+1.0％</t>
+          <t>+4.2％</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
@@ -6411,17 +6411,17 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>+69</t>
+          <t>+71</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -6448,17 +6448,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>150</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>140</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -6485,17 +6485,17 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>349</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>317</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>-32</t>
+          <t>-33</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -6572,12 +6572,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>16136</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>19351</t>
+          <t>19960</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>786</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>956</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>710</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>464</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>218</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>218</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -6827,12 +6827,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>587</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>719</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -6900,17 +6900,17 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>537</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>16136</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -6929,22 +6929,22 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>589</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>15112</t>
+          <t>15604</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>在宅+1.0％／訪問介護-3.4％</t>
+          <t>在宅+1.0％／訪問介護-3.3％</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
@@ -7002,22 +7002,22 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>356</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>15950</t>
+          <t>16451</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
@@ -7031,22 +7031,22 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>349</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>16136</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
@@ -7064,22 +7064,22 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>368</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>16484</t>
+          <t>17002</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>349</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>73.3％</t>
+          <t>75.6％</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>57.0％</t>
+          <t>58.8％</t>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">

--- a/output/第10期計画_将来推計_第2段階_サービス見込量.xlsx
+++ b/output/第10期計画_将来推計_第2段階_サービス見込量.xlsx
@@ -91,14 +91,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -175,12 +175,12 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6333,7 +6333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6416,17 +6416,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>+71</t>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>+42</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>+6.7％</t>
+          <t>+4.0％</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -6453,17 +6453,17 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>-10</t>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>-6.4％</t>
+          <t>+0.7％</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -6490,17 +6490,17 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>-33</t>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>-13</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>-9.3％</t>
+          <t>-3.7％</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>19960</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>+23.7％</t>
+          <t>17333</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>+7.4％</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -6590,11 +6590,7 @@
           <t>47→51→55</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>感度が大きい</t>
-        </is>
-      </c>
+      <c r="G12" s="7" t="inlineStr"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -6614,12 +6610,12 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>1467</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>+13.1％</t>
+          <t>1316</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>+1.5％</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -6627,11 +6623,7 @@
           <t>8→8→8</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>感度が大きい</t>
-        </is>
-      </c>
+      <c r="G13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -6651,12 +6643,12 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>956</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>+21.7％</t>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>+5.2％</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -6664,11 +6656,7 @@
           <t>11→11→12</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>感度が大きい</t>
-        </is>
-      </c>
+      <c r="G14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -6688,12 +6676,12 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>-34.7％</t>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>-10.0％</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -6701,11 +6689,7 @@
           <t>10→9→9</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>感度が大きい</t>
-        </is>
-      </c>
+      <c r="G15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -6725,12 +6709,12 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>+9.8％</t>
+          <t>+3.9％</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -6795,12 +6779,12 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>43</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>-40.0％</t>
+          <t>-10.0％</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -6832,12 +6816,12 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>+22.6％</t>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>+6.1％</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -6845,11 +6829,7 @@
           <t>7→7→8</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>感度が大きい</t>
-        </is>
-      </c>
+      <c r="G19" s="7" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
@@ -6942,7 +6922,7 @@
           <t>15604</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>在宅+1.0％／訪問介護-3.3％</t>
         </is>
@@ -7085,19 +7065,118 @@
       <c r="F30" s="7" t="inlineStr"/>
       <c r="G30" s="7" t="inlineStr"/>
     </row>
-    <row r="32" ht="104" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>注1）見込量を最も動かすのは1人当たりの利用日数・回数の趨勢である（②）。訪問介護は直近3年で年平均4回増えており、これを4年延長すると令和11年度の見込量が大きく変わる。注2）利用率の趨勢（①）と認定者数のシナリオ（④）の影響はいずれも数％にとどまる。注3）要介護度別の構成比（③）は、要介護1が増えると在宅の利用者数は増えるが訪問介護の見込量は減る。要介護1の1人当たり利用回数（24回）が要介護5（114回）より大幅に少ないためである。注3-2）1人当たりの趨勢は要介護度別に延長している。このため、実数の小さい種別（短期入所療養介護46日／月、通所介護688日／月等）では、要介護度別の振れが増幅され、合計の推移（短期入所療養介護は令和5〜7年度とも6日で横ばい）と乖離することがある。感度分析は実数の大きい訪問介護（15,645回／月）で読む。注4）本シートの趨勢は直近3年（令和5〜7年度）の年平均変化による。令和7年度は11か月分であるため、確定値が出た時点で再計算する。注5）感度分析は前提の影響の大きさを確認するためのものであり、いずれかを採用値とするものではない。採用値は発注者のご意向と委員会の審議による。</t>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>【⑤ 上限1.1・下限0.9の制約（国のガイドによる）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>対象の項目数</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>制約が働いた項目数</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>うち上限</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>うち下限</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>区分別の利用率</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="C34" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>在宅・居住系・施設×要介護度別。令和11年度の値で判定した</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>1人当たりの利用日数・回数</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="C35" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>サービス種別×要介護度別。同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>国の「自然体推計の計算過程確認シートのガイド」（14.0次リリース版）は、要介護認定率及びサービス利用率の自然体推計に、基準年度の実績×1.1を上限、×0.9を下限とする制約を課しています。令和8年8月31日の点検により、本シートの趨勢にも同じ制約を適用しました（延べ48件・上限31件／下限17件）。制約を掛けない場合、居住系の要介護4は基準年度の0.300倍、要支援1は1.643倍となり、自然体推計として成り立ちません。第1段階の認定率の3シナリオはいずれも制約の範囲内です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="104" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>注1）見込量を最も動かすのは1人当たりの利用日数・回数の趨勢である（②）。訪問介護は直近3年で年平均4回増えており、これを4年延長すると令和11年度の見込量が大きく変わる。注2）利用率の趨勢（①）と認定者数のシナリオ（④）の影響はいずれも数％にとどまる。注3）要介護度別の構成比（③）は、要介護1が増えると在宅の利用者数は増えるが訪問介護の見込量は減る。要介護1の1人当たり利用回数（24回）が要介護5（114回）より大幅に少ないためである。注3-2）1人当たりの趨勢は要介護度別に延長している。このため、実数の小さい種別（短期入所療養介護46日／月、通所介護688日／月等）では、要介護度別の振れが増幅され、合計の推移（短期入所療養介護は令和5〜7年度とも6日で横ばい）と乖離することがある。感度分析は実数の大きい訪問介護（15,645回／月）で読む。注4）本シートの趨勢は直近3年（令和5〜7年度）の年平均変化による。令和7年度は11か月分であるため、確定値が出た時点で再計算する。注5）感度分析は前提の影響の大きさを確認するためのものであり、いずれかを採用値とするものではない。採用値は発注者のご意向と委員会の審議による。注6）⑤のとおり、趨勢には国のガイドによる上限1.1・下限0.9を適用している。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A36:G36"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
